--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>30595.88</v>
+        <v>30456.02</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>22556.69</v>
+        <v>22421.5</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12202.07</v>
+        <v>12128.94</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>42179.8</v>
+        <v>41927.01</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2711.58</v>
+        <v>2695.33</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5067.1</v>
+        <v>5036.73</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2224.39</v>
+        <v>2211.06</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7545.45</v>
+        <v>7500.23</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8756.59</v>
+        <v>8704.110000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7646.53</v>
+        <v>7600.7</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>835</v>
+        <v>830</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4515.6</v>
+        <v>4488.54</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8660.280000000001</v>
+        <v>8608.379999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>18326.5</v>
+        <v>18216.67</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>948.92</v>
+        <v>943.23</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1217.85</v>
+        <v>1210.55</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3931.37</v>
+        <v>3907.81</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7006.5</v>
+        <v>6964.51</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15095.29</v>
+        <v>15004.82</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>28683.5</v>
+        <v>28511.6</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4091.25</v>
+        <v>4066.73</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7376.28</v>
+        <v>7332.07</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>862.4400000000001</v>
+        <v>857.27</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7477.38</v>
+        <v>7432.57</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>784.85</v>
+        <v>780.15</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21612.91</v>
+        <v>21483.38</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2176.56</v>
+        <v>2163.52</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3341.98</v>
+        <v>3321.95</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1145.27</v>
+        <v>1138.41</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2750.49</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8888.17</v>
+        <v>8834.9</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>76716.75999999999</v>
+        <v>76256.99000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4256.89</v>
+        <v>4231.38</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1040.82</v>
+        <v>1034.58</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1330.06</v>
+        <v>1322.09</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1205.86</v>
+        <v>1198.63</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4301.03</v>
+        <v>4275.26</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32841.06</v>
+        <v>32644.24</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4405.9</v>
+        <v>4379.5</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5618.33</v>
+        <v>5584.65</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3944.04</v>
+        <v>3890.42</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2454.58</v>
+        <v>2421.21</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1675.45</v>
+        <v>1652.68</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10604.55</v>
+        <v>10460.38</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>10712.67</v>
+        <v>10567.03</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>910.5700000000001</v>
+        <v>898.1900000000001</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9034.389999999999</v>
+        <v>8911.559999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1060.43</v>
+        <v>1046.01</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3197.57</v>
+        <v>3154.1</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5101.86</v>
+        <v>5032.49</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5186.56</v>
+        <v>5116.04</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3507.54</v>
+        <v>3459.85</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3065.49</v>
+        <v>3023.81</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5187.74</v>
+        <v>5117.21</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1675.13</v>
+        <v>1652.36</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>20397.91</v>
+        <v>20120.59</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>909.15</v>
+        <v>896.79</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>37036.26</v>
+        <v>36532.73</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1680.4</v>
+        <v>1657.56</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2792.45</v>
+        <v>2754.49</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2502.25</v>
+        <v>2468.23</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>58873.15</v>
+        <v>58072.73</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1381.54</v>
+        <v>1362.76</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1939.59</v>
+        <v>1913.22</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2028.24</v>
+        <v>2000.66</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>990.77</v>
+        <v>977.3</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2403.47</v>
+        <v>2370.79</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5019.11</v>
+        <v>4950.87</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7984.34</v>
+        <v>7875.79</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1322.73</v>
+        <v>1304.75</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1022.94</v>
+        <v>1009.03</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>797.24</v>
+        <v>786.4</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5091.46</v>
+        <v>5022.24</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1228.46</v>
+        <v>1211.76</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2268.54</v>
+        <v>2237.7</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3340.22</v>
+        <v>3294.8</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7722.74</v>
+        <v>7656.87</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>11143.44</v>
+        <v>11048.4</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>932.4299999999999</v>
+        <v>924.48</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1121.33</v>
+        <v>1111.77</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2424.21</v>
+        <v>2403.53</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>9749.209999999999</v>
+        <v>9666.059999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1022.86</v>
+        <v>1014.13</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1458.47</v>
+        <v>1446.03</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1809.58</v>
+        <v>1794.15</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>994.78</v>
+        <v>986.3</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2182.03</v>
+        <v>2163.42</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>48502.03</v>
+        <v>48088.34</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1575.1</v>
+        <v>1561.67</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2135.12</v>
+        <v>2116.91</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2001.15</v>
+        <v>1984.08</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>20319.28</v>
+        <v>20145.97</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>12912.32</v>
+        <v>12802.19</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4989.68</v>
+        <v>4947.12</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3016.1</v>
+        <v>2990.38</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6364.34</v>
+        <v>6310.06</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2214.48</v>
+        <v>2195.59</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1808.79</v>
+        <v>1793.36</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4738.06</v>
+        <v>4697.65</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1424.17</v>
+        <v>1412.03</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8130.61</v>
+        <v>8061.26</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3124.15</v>
+        <v>3097.51</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>9979.35</v>
+        <v>9894.23</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2205.07</v>
+        <v>2186.26</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3931.16</v>
+        <v>3897.63</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5876.3</v>
+        <v>5826.18</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2479.06</v>
+        <v>2457.92</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3960.69</v>
+        <v>3926.9</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>28070.31</v>
+        <v>27830.89</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>942.5700000000001</v>
+        <v>934.53</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>812.59</v>
+        <v>805.66</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>194324.36</v>
+        <v>192666.9</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2707.22</v>
+        <v>2684.13</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>810.77</v>
+        <v>803.86</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>69122.95</v>
+        <v>68533.38</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5667.25</v>
+        <v>5618.91</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>848.37</v>
+        <v>841.13</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2081.31</v>
+        <v>2063.56</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4632.53</v>
+        <v>4593.02</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15826.07</v>
+        <v>15691.09</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12844.89</v>
+        <v>12735.33</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2979</v>
+        <v>2953.6</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>937.6</v>
+        <v>929.61</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1437.72</v>
+        <v>1445.47</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>10203.82</v>
+        <v>10258.77</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>8475.4</v>
+        <v>8521.040000000001</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4350.54</v>
+        <v>4373.96</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>787.25</v>
+        <v>791.49</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>813.29</v>
+        <v>817.67</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3073.95</v>
+        <v>3090.51</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1005.46</v>
+        <v>1010.88</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4994.95</v>
+        <v>5021.84</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>8198.25</v>
+        <v>8242.4</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4689.23</v>
+        <v>4714.49</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1516.77</v>
+        <v>1524.94</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4508.71</v>
+        <v>4532.99</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3347.37</v>
+        <v>3365.4</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>10499.56</v>
+        <v>10556.1</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1002.22</v>
+        <v>1007.62</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2012.3</v>
+        <v>2023.14</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2161.12</v>
+        <v>2172.76</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1718.11</v>
+        <v>1727.36</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>23266.06</v>
+        <v>23391.35</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1323.89</v>
+        <v>1331.02</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>14927.06</v>
+        <v>15007.44</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2357.1</v>
+        <v>2369.79</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2543.37</v>
+        <v>2557.07</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1762.79</v>
+        <v>1772.28</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3141.28</v>
+        <v>3158.19</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>52983.43</v>
+        <v>53268.75</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5436.12</v>
+        <v>5465.39</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>16559.91</v>
+        <v>16649.08</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1747.95</v>
+        <v>1757.37</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>6247.74</v>
+        <v>6281.38</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>790.5</v>
+        <v>794.76</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2803.9</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>870.27</v>
+        <v>874.96</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8539.450000000001</v>
+        <v>8585.440000000001</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1613.11</v>
+        <v>1621.8</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>19749.92</v>
+        <v>19856.27</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1271.56</v>
+        <v>1278.41</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>9840.950000000001</v>
+        <v>9893.940000000001</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>797.1799999999999</v>
+        <v>801.48</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5382.08</v>
+        <v>5411.06</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>28402.02</v>
+        <v>28554.96</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>799.5599999999999</v>
+        <v>803.87</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>33389.73</v>
+        <v>33763.15</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>982.53</v>
+        <v>993.52</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>16333.36</v>
+        <v>16516.03</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>21616.29</v>
+        <v>21858.04</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>4787.29</v>
+        <v>4840.83</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>15938.7</v>
+        <v>16116.95</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>812.67</v>
+        <v>821.76</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1830.74</v>
+        <v>1851.22</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1919.1</v>
+        <v>1940.56</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1324.4</v>
+        <v>1339.21</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2974.64</v>
+        <v>3007.91</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3331.16</v>
+        <v>3368.41</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7918.42</v>
+        <v>8006.97</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>43075.69</v>
+        <v>43557.44</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1146.13</v>
+        <v>1158.94</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>6900.36</v>
+        <v>6977.53</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3292.11</v>
+        <v>3328.93</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1670.92</v>
+        <v>1689.61</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3969.48</v>
+        <v>4013.88</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2061.09</v>
+        <v>2084.15</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6470.44</v>
+        <v>6542.8</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1066.99</v>
+        <v>1078.93</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1254.38</v>
+        <v>1268.41</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2907.26</v>
+        <v>2939.78</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2227.92</v>
+        <v>2252.84</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1669.65</v>
+        <v>1688.33</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2812.46</v>
+        <v>2843.92</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5497.68</v>
+        <v>5559.17</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1530.79</v>
+        <v>1547.91</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2781.8</v>
+        <v>2812.91</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1725.94</v>
+        <v>1745.24</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>5622.37</v>
+        <v>5685.25</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>876.29</v>
+        <v>886.09</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>4761.76</v>
+        <v>4815.02</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>3641.7</v>
+        <v>3682.43</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4674.99</v>
+        <v>4727.28</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4705.99</v>
+        <v>4758.62</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>6680.17</v>
+        <v>6754.88</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4852.71</v>
+        <v>4906.99</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>57270.31</v>
+        <v>57910.8</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5705.42</v>
+        <v>5769.23</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1675.37</v>
+        <v>1694.1</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>7834.9</v>
+        <v>7922.52</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1493.07</v>
+        <v>1509.77</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2365.58</v>
+        <v>2392.04</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1677.6</v>
+        <v>1696.36</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>18998.33</v>
+        <v>19210.8</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>980.2</v>
+        <v>991.16</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2083.99</v>
+        <v>2107.3</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2252.62</v>
+        <v>2277.81</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>16715.77</v>
+        <v>16902.72</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3525.64</v>
+        <v>3565.07</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>12615.38</v>
+        <v>12756.46</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2895.06</v>
+        <v>2927.43</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>969.75</v>
+        <v>980.6</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3817.9</v>
+        <v>3846.82</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1693.19</v>
+        <v>1706.01</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4932.89</v>
+        <v>4970.25</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2348.28</v>
+        <v>2366.07</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>7647.81</v>
+        <v>7705.74</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3614.15</v>
+        <v>3641.53</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1931.69</v>
+        <v>1946.32</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1453.9</v>
+        <v>1464.91</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3838.19</v>
+        <v>3867.26</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>5237.85</v>
+        <v>5277.52</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2355.44</v>
+        <v>2373.28</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1122.97</v>
+        <v>1131.47</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>11753.76</v>
+        <v>11842.79</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11962.49</v>
+        <v>12053.09</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>4352.54</v>
+        <v>4385.51</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2449.57</v>
+        <v>2468.13</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3413.13</v>
+        <v>3438.98</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2210.84</v>
+        <v>2227.59</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2221.09</v>
+        <v>2237.92</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2827.72</v>
+        <v>2849.14</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>12404.71</v>
+        <v>12498.67</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>9942.33</v>
+        <v>10017.64</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1853.33</v>
+        <v>1867.37</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1263.39</v>
+        <v>1272.96</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>10933.46</v>
+        <v>11016.27</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>5036.15</v>
+        <v>5074.29</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>56130.84</v>
+        <v>56556</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>7993.05</v>
+        <v>8053.59</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>3188.1</v>
+        <v>3212.25</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3080.67</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>24639.49</v>
+        <v>24826.12</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>6425.81</v>
+        <v>6474.48</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>10363.73</v>
+        <v>10442.23</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1493.5</v>
+        <v>1504.81</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>7822.36</v>
+        <v>7881.61</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>19125.64</v>
+        <v>19270.5</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>850.11</v>
+        <v>856.55</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1054.57</v>
+        <v>1062.56</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>7012.44</v>
+        <v>7065.55</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>18433.22</v>
+        <v>18572.84</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3283.71</v>
+        <v>3308.58</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1960.5</v>
+        <v>1975.35</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>852.6900000000001</v>
+        <v>859.15</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>793.84</v>
+        <v>799.85</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1517.66</v>
+        <v>1529.15</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1021.78</v>
+        <v>1029.52</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2243.08</v>
+        <v>2260.07</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>44297.13</v>
+        <v>44632.65</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4017.18</v>
+        <v>4047.61</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>828.17</v>
+        <v>831.3</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>6885.43</v>
+        <v>6911.51</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>11879.84</v>
+        <v>11924.85</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>6597.09</v>
+        <v>6622.08</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3274.75</v>
+        <v>3287.15</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2305.62</v>
+        <v>2314.36</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>10695.96</v>
+        <v>10736.48</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>4025.44</v>
+        <v>4040.69</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>900.66</v>
+        <v>904.08</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1364.9</v>
+        <v>1370.07</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>837.98</v>
+        <v>841.15</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>26022.13</v>
+        <v>26120.71</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>842.88</v>
+        <v>846.0700000000001</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2457.85</v>
+        <v>2467.16</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>788.98</v>
+        <v>791.97</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1579.07</v>
+        <v>1585.05</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>8554.75</v>
+        <v>8587.16</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>18560.35</v>
+        <v>18630.66</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1927.6</v>
+        <v>1934.9</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1953.45</v>
+        <v>1960.85</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1411.99</v>
+        <v>1417.34</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3206.13</v>
+        <v>3218.28</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>7517.84</v>
+        <v>7546.32</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>7692.25</v>
+        <v>7721.39</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1799.96</v>
+        <v>1806.78</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2780.71</v>
+        <v>2791.25</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>4496.82</v>
+        <v>4513.86</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1031.72</v>
+        <v>1035.62</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>4035.39</v>
+        <v>4050.67</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2174.83</v>
+        <v>2183.07</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2395.11</v>
+        <v>2404.19</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1300.11</v>
+        <v>1305.03</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>10276.84</v>
+        <v>10315.77</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2386.26</v>
+        <v>2395.3</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>4737.79</v>
+        <v>4755.74</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>4985.53</v>
+        <v>5004.41</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2627.41</v>
+        <v>2637.36</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2665.06</v>
+        <v>2675.15</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>786.41</v>
+        <v>789.39</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1437.42</v>
+        <v>1442.87</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2324.26</v>
+        <v>2333.06</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>7613.53</v>
+        <v>7642.37</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>8921.76</v>
+        <v>8955.559999999999</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3312.33</v>
+        <v>3324.88</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>859.3099999999999</v>
+        <v>862.5599999999999</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>4895.18</v>
+        <v>4913.73</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3338.32</v>
+        <v>3350.97</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2227.07</v>
+        <v>2235.5</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3902.85</v>
+        <v>3917.64</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1016.38</v>
+        <v>1020.23</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>16246.8</v>
+        <v>16308.36</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>5022.38</v>
+        <v>5041.41</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1894.66</v>
+        <v>1901.84</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4424.61</v>
+        <v>4441.37</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>946.36</v>
+        <v>949.95</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1062.36</v>
+        <v>1066.39</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>8912.74</v>
+        <v>8890.24</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3098.07</v>
+        <v>3090.25</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1499.37</v>
+        <v>1495.58</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4597.84</v>
+        <v>4586.23</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>936.9400000000001</v>
+        <v>934.5700000000001</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>6549.22</v>
+        <v>6532.68</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>788.6900000000001</v>
+        <v>786.6900000000001</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>10021.21</v>
+        <v>9995.91</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>4574.47</v>
+        <v>4562.92</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>9588.280000000001</v>
+        <v>9564.07</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>938.03</v>
+        <v>935.66</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2896.2</v>
+        <v>2888.88</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>966.02</v>
+        <v>963.58</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2195.44</v>
+        <v>2189.9</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2005.45</v>
+        <v>2000.38</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>8968.389999999999</v>
+        <v>8945.74</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>10154.49</v>
+        <v>10128.85</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1346.9</v>
+        <v>1343.5</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1341.48</v>
+        <v>1338.09</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>13229.44</v>
+        <v>13196.04</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2863.32</v>
+        <v>2856.09</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1807</v>
+        <v>1802.44</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2715.38</v>
+        <v>2708.52</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>10390.44</v>
+        <v>10364.21</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1531.73</v>
+        <v>1527.86</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2696.16</v>
+        <v>2689.35</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1204.42</v>
+        <v>1201.38</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2723.37</v>
+        <v>2716.5</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1569.52</v>
+        <v>1565.55</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>4305.83</v>
+        <v>4294.96</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>6743.48</v>
+        <v>6726.46</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1282.42</v>
+        <v>1279.18</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>6594.1</v>
+        <v>6577.45</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>4200.27</v>
+        <v>4189.67</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1562.36</v>
+        <v>1558.41</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>835.4299999999999</v>
+        <v>833.3200000000001</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>5098.52</v>
+        <v>5085.65</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>8262.83</v>
+        <v>8241.969999999999</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>4977.99</v>
+        <v>4965.42</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>70360.74000000001</v>
+        <v>70183.10000000001</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>4350.81</v>
+        <v>4339.82</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2142.27</v>
+        <v>2136.86</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>8754.219999999999</v>
+        <v>8837.389999999999</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>2249.26</v>
+        <v>2270.63</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>9699.6</v>
+        <v>9791.75</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>3342.08</v>
+        <v>3373.83</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>6530.21</v>
+        <v>6592.25</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>995.01</v>
+        <v>1004.46</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>8556.629999999999</v>
+        <v>8637.93</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1107.23</v>
+        <v>1117.75</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>3567.99</v>
+        <v>3601.89</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1243.27</v>
+        <v>1255.08</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2625.39</v>
+        <v>2650.33</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>8369.98</v>
+        <v>8449.5</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1643.14</v>
+        <v>1658.75</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>787.04</v>
+        <v>794.51</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1598.9</v>
+        <v>1614.09</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>33390.02</v>
+        <v>33707.25</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2426.64</v>
+        <v>2449.7</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>982.14</v>
+        <v>991.47</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1854.27</v>
+        <v>1871.89</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3572.79</v>
+        <v>3606.74</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>16675.27</v>
+        <v>16833.7</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>13828.39</v>
+        <v>13959.77</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>9646.91</v>
+        <v>9738.559999999999</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>5044.06</v>
+        <v>5091.98</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3812.74</v>
+        <v>3848.97</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>789.95</v>
+        <v>797.45</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>928.6</v>
+        <v>937.4299999999999</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1399.54</v>
+        <v>1412.84</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1375.74</v>
+        <v>1388.81</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3665.84</v>
+        <v>3700.67</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>945.33</v>
+        <v>954.3099999999999</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>4072.12</v>
+        <v>4110.81</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>24373.17</v>
+        <v>24604.73</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>5560.47</v>
+        <v>5613.3</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>7574.04</v>
+        <v>7646</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>7530.65</v>
+        <v>7602.19</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>3885.44</v>
+        <v>3922.35</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>4845.33</v>
+        <v>4891.36</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>814.8</v>
+        <v>822.54</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>4030.4</v>
+        <v>4068.69</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>3146.45</v>
+        <v>3176.34</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1175.85</v>
+        <v>1187.02</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2834.46</v>
+        <v>2861.39</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>792.74</v>
+        <v>800.27</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>7039.52</v>
+        <v>7106.4</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1381.54</v>
+        <v>1394.66</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>5882.73</v>
+        <v>5938.62</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>1050.17</v>
+        <v>1060.15</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2518.77</v>
+        <v>2542.7</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>3720.98</v>
+        <v>3756.33</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2120.19</v>
+        <v>2140.34</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>829.39</v>
+        <v>837.27</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>1404.4</v>
+        <v>1417.74</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>817.8</v>
+        <v>825.5700000000001</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>802</v>
+        <v>809.62</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2570.34</v>
+        <v>2594.76</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2915.35</v>
+        <v>2943.05</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>2415.1</v>
+        <v>2433.09</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>4045.13</v>
+        <v>4075.27</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1971.86</v>
+        <v>1986.55</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>6197.72</v>
+        <v>6243.89</v>
       </c>
     </row>
     <row r="431">
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>3623.58</v>
+        <v>3650.58</v>
       </c>
     </row>
     <row r="432">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>5833.3</v>
+        <v>5876.76</v>
       </c>
     </row>
     <row r="433">
@@ -26872,7 +26872,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>578.8</v>
+        <v>583.11</v>
       </c>
     </row>
     <row r="434">
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>16708.4</v>
+        <v>16832.88</v>
       </c>
     </row>
     <row r="435">
@@ -26994,7 +26994,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>3201.82</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="436">
@@ -27055,7 +27055,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1097.68</v>
+        <v>1105.86</v>
       </c>
     </row>
     <row r="437">
@@ -27116,7 +27116,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>6684.21</v>
+        <v>6734</v>
       </c>
     </row>
     <row r="438">
@@ -27177,7 +27177,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>2818.97</v>
+        <v>2839.97</v>
       </c>
     </row>
     <row r="439">
@@ -27238,7 +27238,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>7114.54</v>
+        <v>7167.54</v>
       </c>
     </row>
     <row r="440">
@@ -27299,7 +27299,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>799.66</v>
+        <v>805.62</v>
       </c>
     </row>
     <row r="441">
@@ -27360,7 +27360,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>4214.68</v>
+        <v>4246.08</v>
       </c>
     </row>
     <row r="442">
@@ -27421,7 +27421,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>1037.98</v>
+        <v>1045.72</v>
       </c>
     </row>
     <row r="443">
@@ -27482,7 +27482,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>5434.71</v>
+        <v>5475.2</v>
       </c>
     </row>
     <row r="444">
@@ -27543,7 +27543,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>14319.75</v>
+        <v>14426.43</v>
       </c>
     </row>
     <row r="445">
@@ -27604,7 +27604,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>878.5599999999999</v>
+        <v>885.11</v>
       </c>
     </row>
     <row r="446">
@@ -27665,7 +27665,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>2016.8</v>
+        <v>2031.83</v>
       </c>
     </row>
     <row r="447">
@@ -27726,7 +27726,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2950.14</v>
+        <v>2972.12</v>
       </c>
     </row>
     <row r="448">
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>786.76</v>
+        <v>792.62</v>
       </c>
     </row>
     <row r="449">
@@ -27848,7 +27848,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>1172.07</v>
+        <v>1180.8</v>
       </c>
     </row>
     <row r="450">
@@ -27909,7 +27909,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>9306.43</v>
+        <v>9375.76</v>
       </c>
     </row>
     <row r="451">
@@ -27970,7 +27970,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>2784.21</v>
+        <v>2804.95</v>
       </c>
     </row>
     <row r="452">
@@ -28031,7 +28031,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>28104.87</v>
+        <v>28314.25</v>
       </c>
     </row>
     <row r="453">
@@ -28096,7 +28096,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>51527.74</v>
+        <v>51911.62</v>
       </c>
     </row>
     <row r="454">
@@ -28157,7 +28157,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2254.84</v>
+        <v>2271.64</v>
       </c>
     </row>
     <row r="455">
@@ -28218,7 +28218,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>834.46</v>
+        <v>840.6799999999999</v>
       </c>
     </row>
     <row r="456">
@@ -28279,7 +28279,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>2016.13</v>
+        <v>2031.15</v>
       </c>
     </row>
     <row r="457">
@@ -28340,7 +28340,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>892.9400000000001</v>
+        <v>899.59</v>
       </c>
     </row>
     <row r="458">
@@ -28401,7 +28401,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>4460.32</v>
+        <v>4493.55</v>
       </c>
     </row>
     <row r="459">
@@ -28462,7 +28462,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>798.22</v>
+        <v>804.17</v>
       </c>
     </row>
     <row r="460">
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>1250.92</v>
+        <v>1260.24</v>
       </c>
     </row>
     <row r="461">
@@ -28584,7 +28584,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>5293.26</v>
+        <v>5332.7</v>
       </c>
     </row>
     <row r="462">
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>13841.88</v>
+        <v>13945</v>
       </c>
     </row>
     <row r="463">
@@ -28706,7 +28706,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>6175.28</v>
+        <v>6221.28</v>
       </c>
     </row>
     <row r="464">
@@ -28767,7 +28767,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>2431.87</v>
+        <v>2449.98</v>
       </c>
     </row>
     <row r="465">
@@ -28828,7 +28828,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>4457.86</v>
+        <v>4491.07</v>
       </c>
     </row>
     <row r="466">
@@ -28889,7 +28889,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>5612.49</v>
+        <v>5654.3</v>
       </c>
     </row>
     <row r="467">
@@ -28950,7 +28950,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>9389.940000000001</v>
+        <v>9459.9</v>
       </c>
     </row>
     <row r="468">
@@ -29011,7 +29011,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>12039.49</v>
+        <v>12129.19</v>
       </c>
     </row>
     <row r="469">
@@ -29072,7 +29072,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2652.73</v>
+        <v>2672.49</v>
       </c>
     </row>
     <row r="470">
@@ -29133,7 +29133,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2303.8</v>
+        <v>2320.97</v>
       </c>
     </row>
     <row r="471">
@@ -29194,7 +29194,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1448.84</v>
+        <v>1459.63</v>
       </c>
     </row>
     <row r="472">
@@ -29255,7 +29255,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>1267.38</v>
+        <v>1276.82</v>
       </c>
     </row>
     <row r="473">
@@ -29316,7 +29316,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>6168.09</v>
+        <v>6214.04</v>
       </c>
     </row>
     <row r="474">
@@ -29377,7 +29377,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>6148.21</v>
+        <v>6194.01</v>
       </c>
     </row>
     <row r="475">
@@ -29438,7 +29438,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>2520.02</v>
+        <v>2538.79</v>
       </c>
     </row>
     <row r="476">
@@ -29499,7 +29499,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>7958.69</v>
+        <v>8017.98</v>
       </c>
     </row>
     <row r="477">
@@ -29560,7 +29560,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>2189.26</v>
+        <v>2205.57</v>
       </c>
     </row>
     <row r="478">
@@ -29621,7 +29621,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>829.8200000000001</v>
+        <v>836.01</v>
       </c>
     </row>
     <row r="479">
@@ -29682,7 +29682,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>807.24</v>
+        <v>813.26</v>
       </c>
     </row>
     <row r="480">
@@ -29743,7 +29743,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>16205.55</v>
+        <v>16326.28</v>
       </c>
     </row>
     <row r="481">
@@ -29804,7 +29804,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>2978.34</v>
+        <v>3000.53</v>
       </c>
     </row>
     <row r="482">
@@ -29865,7 +29865,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>5432.33</v>
+        <v>5472.8</v>
       </c>
     </row>
     <row r="483">
@@ -29926,7 +29926,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>4661.82</v>
+        <v>4696.55</v>
       </c>
     </row>
     <row r="484">
@@ -29987,7 +29987,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>3434.59</v>
+        <v>3460.18</v>
       </c>
     </row>
     <row r="485">
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>4080.51</v>
+        <v>4110.91</v>
       </c>
     </row>
     <row r="486">
@@ -30109,7 +30109,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>1509.31</v>
+        <v>1520.56</v>
       </c>
     </row>
     <row r="487">
@@ -30170,7 +30170,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>4268.06</v>
+        <v>4225.5</v>
       </c>
     </row>
     <row r="488">
@@ -30231,7 +30231,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>7670.41</v>
+        <v>7593.91</v>
       </c>
     </row>
     <row r="489">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>2416.63</v>
+        <v>2392.53</v>
       </c>
     </row>
     <row r="490">
@@ -30353,7 +30353,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1104.47</v>
+        <v>1093.45</v>
       </c>
     </row>
     <row r="491">
@@ -30414,7 +30414,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>6157.22</v>
+        <v>6095.81</v>
       </c>
     </row>
     <row r="492">
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>1574.93</v>
+        <v>1559.23</v>
       </c>
     </row>
     <row r="493">
@@ -30536,7 +30536,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1028.46</v>
+        <v>1018.2</v>
       </c>
     </row>
     <row r="494">
@@ -30597,7 +30597,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>1960.16</v>
+        <v>1940.61</v>
       </c>
     </row>
     <row r="495">
@@ -30658,7 +30658,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>1950.73</v>
+        <v>1931.28</v>
       </c>
     </row>
     <row r="496">
@@ -30719,7 +30719,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>2232.64</v>
+        <v>2210.37</v>
       </c>
     </row>
     <row r="497">
@@ -30780,7 +30780,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>797.84</v>
+        <v>789.89</v>
       </c>
     </row>
     <row r="498">
@@ -30841,7 +30841,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>990.87</v>
+        <v>980.99</v>
       </c>
     </row>
     <row r="499">
@@ -30902,7 +30902,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2263.85</v>
+        <v>2241.27</v>
       </c>
     </row>
     <row r="500">
@@ -30963,7 +30963,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1694.96</v>
+        <v>1678.05</v>
       </c>
     </row>
     <row r="501">
@@ -31024,7 +31024,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1310.23</v>
+        <v>1297.17</v>
       </c>
     </row>
     <row r="502">
@@ -31085,7 +31085,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>800.99</v>
+        <v>793</v>
       </c>
     </row>
     <row r="503">
@@ -31146,7 +31146,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1205</v>
+        <v>1192.98</v>
       </c>
     </row>
     <row r="504">
@@ -31207,7 +31207,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>4168.11</v>
+        <v>4126.55</v>
       </c>
     </row>
     <row r="505">
@@ -31268,7 +31268,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2383.01</v>
+        <v>2359.25</v>
       </c>
     </row>
     <row r="506">
@@ -31329,7 +31329,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>7292.53</v>
+        <v>7219.8</v>
       </c>
     </row>
     <row r="507">
@@ -31390,7 +31390,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1917.19</v>
+        <v>1898.07</v>
       </c>
     </row>
     <row r="508">
@@ -31451,7 +31451,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1419.72</v>
+        <v>1405.56</v>
       </c>
     </row>
     <row r="509">
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>8207.639999999999</v>
+        <v>8125.79</v>
       </c>
     </row>
     <row r="510">
@@ -31573,7 +31573,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>12366.77</v>
+        <v>12243.44</v>
       </c>
     </row>
     <row r="511">
@@ -31638,7 +31638,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>238524.74</v>
+        <v>236145.99</v>
       </c>
     </row>
     <row r="512">
@@ -31699,7 +31699,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>6511.94</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="513">
@@ -31760,7 +31760,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>815.11</v>
+        <v>806.98</v>
       </c>
     </row>
     <row r="514">
@@ -31821,7 +31821,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>16901.66</v>
+        <v>16733.11</v>
       </c>
     </row>
     <row r="515">
@@ -31882,7 +31882,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>6766.78</v>
+        <v>6699.3</v>
       </c>
     </row>
     <row r="516">
@@ -31943,7 +31943,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>787.9</v>
+        <v>780.05</v>
       </c>
     </row>
     <row r="517">
@@ -32004,7 +32004,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2140.08</v>
+        <v>2118.74</v>
       </c>
     </row>
     <row r="518">
@@ -32065,7 +32065,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2144.86</v>
+        <v>2123.47</v>
       </c>
     </row>
     <row r="519">
@@ -32126,7 +32126,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>40013.29</v>
+        <v>39614.25</v>
       </c>
     </row>
     <row r="520">
@@ -32187,7 +32187,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>5188.8</v>
+        <v>5137.05</v>
       </c>
     </row>
     <row r="521">
@@ -32248,7 +32248,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>1515.21</v>
+        <v>1500.1</v>
       </c>
     </row>
     <row r="522">
@@ -32309,7 +32309,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>1514.63</v>
+        <v>1499.52</v>
       </c>
     </row>
     <row r="523">
@@ -32370,7 +32370,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>1718.11</v>
+        <v>1700.97</v>
       </c>
     </row>
     <row r="524">
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1044.79</v>
+        <v>1034.37</v>
       </c>
     </row>
     <row r="525">
@@ -32492,7 +32492,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>4199.92</v>
+        <v>4158.04</v>
       </c>
     </row>
     <row r="526">
@@ -32553,7 +32553,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>3454.51</v>
+        <v>3420.06</v>
       </c>
     </row>
     <row r="527">
@@ -32614,7 +32614,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>826.6799999999999</v>
+        <v>818.4400000000001</v>
       </c>
     </row>
     <row r="528">
@@ -32675,7 +32675,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>25236.92</v>
+        <v>24985.24</v>
       </c>
     </row>
     <row r="529">
@@ -32736,7 +32736,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>24639.49</v>
+        <v>24393.77</v>
       </c>
     </row>
     <row r="530">
@@ -32797,7 +32797,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>5493.34</v>
+        <v>5438.56</v>
       </c>
     </row>
     <row r="531">
@@ -32858,7 +32858,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1806.29</v>
+        <v>1788.28</v>
       </c>
     </row>
     <row r="532">
@@ -32919,7 +32919,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>11238.82</v>
+        <v>11189.56</v>
       </c>
     </row>
     <row r="533">
@@ -32980,7 +32980,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1974.77</v>
+        <v>1966.11</v>
       </c>
     </row>
     <row r="534">
@@ -33041,7 +33041,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>3522.34</v>
+        <v>3506.9</v>
       </c>
     </row>
     <row r="535">
@@ -33102,7 +33102,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1077.64</v>
+        <v>1072.91</v>
       </c>
     </row>
     <row r="536">
@@ -33163,7 +33163,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>4510.49</v>
+        <v>4490.72</v>
       </c>
     </row>
     <row r="537">
@@ -33224,7 +33224,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>924.9</v>
+        <v>920.85</v>
       </c>
     </row>
     <row r="538">
@@ -33285,7 +33285,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>3981.86</v>
+        <v>3964.41</v>
       </c>
     </row>
     <row r="539">
@@ -33346,7 +33346,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1479.86</v>
+        <v>1473.37</v>
       </c>
     </row>
     <row r="540">
@@ -33407,7 +33407,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>7406.36</v>
+        <v>7373.9</v>
       </c>
     </row>
     <row r="541">
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>5187.74</v>
+        <v>5165</v>
       </c>
     </row>
     <row r="542">
@@ -33529,7 +33529,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2737.67</v>
+        <v>2725.67</v>
       </c>
     </row>
     <row r="543">
@@ -33590,7 +33590,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>6079.8</v>
+        <v>6053.15</v>
       </c>
     </row>
     <row r="544">
@@ -33651,7 +33651,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>9836.309999999999</v>
+        <v>9793.190000000001</v>
       </c>
     </row>
     <row r="545">
@@ -33712,7 +33712,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>7158.79</v>
+        <v>7127.41</v>
       </c>
     </row>
     <row r="546">
@@ -33773,7 +33773,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1109.88</v>
+        <v>1105.01</v>
       </c>
     </row>
     <row r="547">
@@ -33834,7 +33834,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2732.47</v>
+        <v>2720.49</v>
       </c>
     </row>
     <row r="548">
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>3352.31</v>
+        <v>3337.62</v>
       </c>
     </row>
     <row r="549">
@@ -33956,7 +33956,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>2948.06</v>
+        <v>2935.14</v>
       </c>
     </row>
     <row r="550">
@@ -34017,7 +34017,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>5409.53</v>
+        <v>5385.81</v>
       </c>
     </row>
     <row r="551">
@@ -34078,7 +34078,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>17146.29</v>
+        <v>17071.13</v>
       </c>
     </row>
     <row r="552">
@@ -34139,7 +34139,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>2730.15</v>
+        <v>2718.18</v>
       </c>
     </row>
     <row r="553">
@@ -34200,7 +34200,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>18711.48</v>
+        <v>18629.46</v>
       </c>
     </row>
     <row r="554">
@@ -34261,7 +34261,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>2252.95</v>
+        <v>2243.07</v>
       </c>
     </row>
     <row r="555">
@@ -34322,7 +34322,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>1282.03</v>
+        <v>1276.41</v>
       </c>
     </row>
     <row r="556">
@@ -34383,7 +34383,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2988.36</v>
+        <v>2975.26</v>
       </c>
     </row>
     <row r="557">
@@ -34444,7 +34444,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>13299.44</v>
+        <v>13241.14</v>
       </c>
     </row>
     <row r="558">
@@ -34505,7 +34505,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>1259.14</v>
+        <v>1253.62</v>
       </c>
     </row>
     <row r="559">
@@ -34566,7 +34566,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>3127.44</v>
+        <v>3113.73</v>
       </c>
     </row>
     <row r="560">
@@ -34627,7 +34627,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2247.88</v>
+        <v>2238.02</v>
       </c>
     </row>
     <row r="561">
@@ -34688,7 +34688,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1097.3</v>
+        <v>1092.49</v>
       </c>
     </row>
     <row r="562">
@@ -34749,7 +34749,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>42356.17</v>
+        <v>42170.5</v>
       </c>
     </row>
     <row r="563">
@@ -34810,7 +34810,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>1656.37</v>
+        <v>1649.11</v>
       </c>
     </row>
     <row r="564">
@@ -34871,7 +34871,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>3370.56</v>
+        <v>3355.79</v>
       </c>
     </row>
     <row r="565">
@@ -34932,7 +34932,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>2948.19</v>
+        <v>2935.26</v>
       </c>
     </row>
     <row r="566">
@@ -34993,7 +34993,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>863.3</v>
+        <v>859.51</v>
       </c>
     </row>
     <row r="567">
@@ -35054,7 +35054,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>1329.31</v>
+        <v>1323.49</v>
       </c>
     </row>
     <row r="568">
@@ -35115,7 +35115,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>6349.7</v>
+        <v>6321.86</v>
       </c>
     </row>
     <row r="569">
@@ -35176,7 +35176,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>805.9299999999999</v>
+        <v>802.4</v>
       </c>
     </row>
     <row r="570">
@@ -35237,7 +35237,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>2019.52</v>
+        <v>2010.67</v>
       </c>
     </row>
     <row r="571">
@@ -35298,7 +35298,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>7385.67</v>
+        <v>7353.29</v>
       </c>
     </row>
     <row r="572">
@@ -35359,7 +35359,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>9194.48</v>
+        <v>9154.18</v>
       </c>
     </row>
     <row r="573">
@@ -35420,7 +35420,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1290.11</v>
+        <v>1284.46</v>
       </c>
     </row>
     <row r="574">
@@ -35481,7 +35481,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>4547.16</v>
+        <v>4497.69</v>
       </c>
     </row>
     <row r="575">
@@ -35542,7 +35542,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>3607.42</v>
+        <v>3568.17</v>
       </c>
     </row>
     <row r="576">
@@ -35603,7 +35603,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>1228.38</v>
+        <v>1215.02</v>
       </c>
     </row>
     <row r="577">
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>3563.39</v>
+        <v>3524.63</v>
       </c>
     </row>
     <row r="578">
@@ -35725,7 +35725,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>2276.54</v>
+        <v>2251.78</v>
       </c>
     </row>
     <row r="579">
@@ -35786,7 +35786,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>7406.96</v>
+        <v>7326.39</v>
       </c>
     </row>
     <row r="580">
@@ -35847,7 +35847,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2074.06</v>
+        <v>2051.5</v>
       </c>
     </row>
     <row r="581">
@@ -35908,7 +35908,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>816.29</v>
+        <v>807.41</v>
       </c>
     </row>
     <row r="582">
@@ -35969,7 +35969,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>3318.59</v>
+        <v>3282.49</v>
       </c>
     </row>
     <row r="583">
@@ -36030,7 +36030,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>2324.49</v>
+        <v>2299.2</v>
       </c>
     </row>
     <row r="584">
@@ -36091,7 +36091,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>837.78</v>
+        <v>828.66</v>
       </c>
     </row>
     <row r="585">
@@ -36152,7 +36152,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>8089.43</v>
+        <v>8001.43</v>
       </c>
     </row>
     <row r="586">
@@ -36213,7 +36213,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>6628.08</v>
+        <v>6555.98</v>
       </c>
     </row>
     <row r="587">
@@ -36274,7 +36274,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>4032.78</v>
+        <v>3988.91</v>
       </c>
     </row>
     <row r="588">
@@ -36335,7 +36335,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2468.59</v>
+        <v>2441.74</v>
       </c>
     </row>
     <row r="589">
@@ -36396,7 +36396,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>5946.91</v>
+        <v>5882.21</v>
       </c>
     </row>
     <row r="590">
@@ -36457,7 +36457,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1664.42</v>
+        <v>1646.31</v>
       </c>
     </row>
     <row r="591">
@@ -36518,7 +36518,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>2408.08</v>
+        <v>2381.88</v>
       </c>
     </row>
     <row r="592">
@@ -36579,7 +36579,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>6167</v>
+        <v>6099.91</v>
       </c>
     </row>
     <row r="593">
@@ -36640,7 +36640,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>1637.29</v>
+        <v>1619.48</v>
       </c>
     </row>
     <row r="594">
@@ -36701,7 +36701,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>938.9299999999999</v>
+        <v>928.71</v>
       </c>
     </row>
     <row r="595">
@@ -36762,7 +36762,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>3027.24</v>
+        <v>2994.31</v>
       </c>
     </row>
     <row r="596">
@@ -36823,7 +36823,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1010.85</v>
+        <v>999.85</v>
       </c>
     </row>
     <row r="597">
@@ -36884,7 +36884,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>2351.13</v>
+        <v>2325.56</v>
       </c>
     </row>
     <row r="598">
@@ -36945,7 +36945,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>4050.91</v>
+        <v>4006.84</v>
       </c>
     </row>
     <row r="599">
@@ -37006,7 +37006,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>1163.83</v>
+        <v>1151.17</v>
       </c>
     </row>
     <row r="600">
@@ -37067,7 +37067,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1047.65</v>
+        <v>1036.25</v>
       </c>
     </row>
     <row r="601">
@@ -37128,7 +37128,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>6073.62</v>
+        <v>6007.55</v>
       </c>
     </row>
     <row r="602">
@@ -37189,7 +37189,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>4788.72</v>
+        <v>4736.63</v>
       </c>
     </row>
     <row r="603">
@@ -37250,7 +37250,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>2760.11</v>
+        <v>2730.09</v>
       </c>
     </row>
     <row r="604">
@@ -37311,7 +37311,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>1942.75</v>
+        <v>1921.62</v>
       </c>
     </row>
     <row r="605">
@@ -37372,7 +37372,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2336.82</v>
+        <v>2311.4</v>
       </c>
     </row>
     <row r="606">
@@ -37433,7 +37433,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>21274.86</v>
+        <v>21043.43</v>
       </c>
     </row>
     <row r="607">
@@ -37494,7 +37494,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1093.7</v>
+        <v>1081.81</v>
       </c>
     </row>
     <row r="608">
@@ -37555,7 +37555,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>3216.24</v>
+        <v>3181.25</v>
       </c>
     </row>
     <row r="609">
@@ -37616,7 +37616,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>843.15</v>
+        <v>833.97</v>
       </c>
     </row>
     <row r="610">
@@ -37677,7 +37677,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>62098.51</v>
+        <v>61422.99</v>
       </c>
     </row>
     <row r="611">
@@ -37738,7 +37738,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2356.62</v>
+        <v>2330.98</v>
       </c>
     </row>
     <row r="612">
@@ -37799,7 +37799,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>971.01</v>
+        <v>960.45</v>
       </c>
     </row>
     <row r="613">
@@ -37860,7 +37860,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>10515.96</v>
+        <v>10401.56</v>
       </c>
     </row>
     <row r="614">
@@ -37921,7 +37921,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>9045.83</v>
+        <v>8947.42</v>
       </c>
     </row>
     <row r="615">
@@ -37982,7 +37982,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>40829.7</v>
+        <v>40385.55</v>
       </c>
     </row>
     <row r="616">
@@ -38043,7 +38043,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>1493.21</v>
+        <v>1476.97</v>
       </c>
     </row>
     <row r="617">
@@ -38104,7 +38104,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>5752.88</v>
+        <v>5690.3</v>
       </c>
     </row>
     <row r="618">
@@ -38165,7 +38165,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>7677.42</v>
+        <v>7593.9</v>
       </c>
     </row>
     <row r="619">
@@ -38226,7 +38226,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>876.29</v>
+        <v>866.75</v>
       </c>
     </row>
     <row r="620">
@@ -38287,7 +38287,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>1039.32</v>
+        <v>1028.02</v>
       </c>
     </row>
     <row r="621">
@@ -38348,7 +38348,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>794.61</v>
+        <v>785.97</v>
       </c>
     </row>
     <row r="622">
@@ -38409,7 +38409,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3467.15</v>
+        <v>3429.43</v>
       </c>
     </row>
     <row r="623">
@@ -38470,7 +38470,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>1530.09</v>
+        <v>1513.45</v>
       </c>
     </row>
     <row r="624">
@@ -38531,7 +38531,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>4467.16</v>
+        <v>4418.56</v>
       </c>
     </row>
     <row r="625">
@@ -38592,7 +38592,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>39852.86</v>
+        <v>39419.33</v>
       </c>
     </row>
     <row r="626">
@@ -38653,7 +38653,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>6208.58</v>
+        <v>6141.04</v>
       </c>
     </row>
     <row r="627">
@@ -38714,7 +38714,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>3119.64</v>
+        <v>3085.7</v>
       </c>
     </row>
     <row r="628">
@@ -38775,7 +38775,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>3348.92</v>
+        <v>3312.49</v>
       </c>
     </row>
     <row r="629">
@@ -38836,7 +38836,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>2379.48</v>
+        <v>2353.59</v>
       </c>
     </row>
     <row r="630">
@@ -38897,7 +38897,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1926.01</v>
+        <v>1905.06</v>
       </c>
     </row>
     <row r="631">
@@ -38958,7 +38958,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>1356.59</v>
+        <v>1341.83</v>
       </c>
     </row>
     <row r="632">
@@ -39019,7 +39019,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>18352.18</v>
+        <v>18152.54</v>
       </c>
     </row>
     <row r="633">
@@ -39080,7 +39080,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>788.75</v>
+        <v>780.17</v>
       </c>
     </row>
     <row r="634">
@@ -39141,7 +39141,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>1113.77</v>
+        <v>1101.66</v>
       </c>
     </row>
     <row r="635">
@@ -39202,7 +39202,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>2770.52</v>
+        <v>2764.23</v>
       </c>
     </row>
     <row r="636">
@@ -39263,7 +39263,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>1113.87</v>
+        <v>1111.34</v>
       </c>
     </row>
     <row r="637">
@@ -39324,7 +39324,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>2865.62</v>
+        <v>2859.12</v>
       </c>
     </row>
     <row r="638">
@@ -39385,7 +39385,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1295.08</v>
+        <v>1292.14</v>
       </c>
     </row>
     <row r="639">
@@ -39446,7 +39446,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>1181.6</v>
+        <v>1178.92</v>
       </c>
     </row>
     <row r="640">
@@ -39507,7 +39507,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>4406.23</v>
+        <v>4396.23</v>
       </c>
     </row>
     <row r="641">
@@ -39568,7 +39568,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2859.05</v>
+        <v>2852.56</v>
       </c>
     </row>
     <row r="642">
@@ -39629,7 +39629,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>4515.21</v>
+        <v>4504.96</v>
       </c>
     </row>
     <row r="643">
@@ -39690,7 +39690,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>3841.31</v>
+        <v>3832.59</v>
       </c>
     </row>
     <row r="644">
@@ -39751,7 +39751,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>1331.8</v>
+        <v>1328.78</v>
       </c>
     </row>
     <row r="645">
@@ -39812,7 +39812,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>2799.56</v>
+        <v>2793.21</v>
       </c>
     </row>
     <row r="646">
@@ -39873,7 +39873,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>2773.9</v>
+        <v>2767.6</v>
       </c>
     </row>
     <row r="647">
@@ -39934,7 +39934,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>4409.28</v>
+        <v>4399.28</v>
       </c>
     </row>
     <row r="648">
@@ -39995,7 +39995,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>11266.17</v>
+        <v>11240.6</v>
       </c>
     </row>
     <row r="649">
@@ -40056,7 +40056,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>1114.03</v>
+        <v>1111.5</v>
       </c>
     </row>
     <row r="650">
@@ -40117,7 +40117,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>4679.93</v>
+        <v>4669.3</v>
       </c>
     </row>
     <row r="651">
@@ -40178,7 +40178,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>1930.19</v>
+        <v>1925.81</v>
       </c>
     </row>
     <row r="652">
@@ -40239,7 +40239,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>2319.45</v>
+        <v>2314.18</v>
       </c>
     </row>
     <row r="653">
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>1144.61</v>
+        <v>1142.01</v>
       </c>
     </row>
     <row r="654">
@@ -40361,7 +40361,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>13997.7</v>
+        <v>13965.92</v>
       </c>
     </row>
     <row r="655">
@@ -40422,7 +40422,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>1137.45</v>
+        <v>1134.87</v>
       </c>
     </row>
     <row r="656">
@@ -40483,7 +40483,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>2744.2</v>
+        <v>2737.97</v>
       </c>
     </row>
     <row r="657">
@@ -40544,7 +40544,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1391.27</v>
+        <v>1388.11</v>
       </c>
     </row>
     <row r="658">
@@ -40605,7 +40605,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>1156.14</v>
+        <v>1153.52</v>
       </c>
     </row>
     <row r="659">
@@ -40666,7 +40666,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1746.11</v>
+        <v>1742.15</v>
       </c>
     </row>
     <row r="660">
@@ -40727,7 +40727,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>3345.41</v>
+        <v>3337.81</v>
       </c>
     </row>
     <row r="661">
@@ -40788,7 +40788,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>17318.42</v>
+        <v>17279.11</v>
       </c>
     </row>
     <row r="662">
@@ -40849,7 +40849,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>924.6</v>
+        <v>922.5</v>
       </c>
     </row>
     <row r="663">
@@ -40910,7 +40910,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>3812.13</v>
+        <v>3803.48</v>
       </c>
     </row>
     <row r="664">
@@ -40971,7 +40971,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>8428.92</v>
+        <v>8409.790000000001</v>
       </c>
     </row>
     <row r="665">
@@ -41032,7 +41032,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>832.41</v>
+        <v>830.35</v>
       </c>
     </row>
     <row r="666">
@@ -41093,7 +41093,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>2004.99</v>
+        <v>2000.04</v>
       </c>
     </row>
     <row r="667">
@@ -41154,7 +41154,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>2623.7</v>
+        <v>2617.22</v>
       </c>
     </row>
     <row r="668">
@@ -41215,7 +41215,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>953.7</v>
+        <v>951.34</v>
       </c>
     </row>
     <row r="669">
@@ -41276,7 +41276,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>809.34</v>
+        <v>807.34</v>
       </c>
     </row>
     <row r="670">
@@ -41337,7 +41337,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>4216.05</v>
+        <v>4205.64</v>
       </c>
     </row>
     <row r="671">
@@ -41398,7 +41398,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>6714.84</v>
+        <v>6698.26</v>
       </c>
     </row>
     <row r="672">
@@ -41459,7 +41459,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>3379.95</v>
+        <v>3371.6</v>
       </c>
     </row>
     <row r="673">
@@ -41520,7 +41520,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>6637.01</v>
+        <v>6620.62</v>
       </c>
     </row>
     <row r="674">
@@ -41581,7 +41581,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>811.98</v>
+        <v>809.98</v>
       </c>
     </row>
     <row r="675">
@@ -41642,7 +41642,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>1850.71</v>
+        <v>1846.14</v>
       </c>
     </row>
     <row r="676">
@@ -41703,7 +41703,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2615.46</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="677">
@@ -41764,7 +41764,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>819.28</v>
+        <v>817.26</v>
       </c>
     </row>
     <row r="678">
@@ -41825,7 +41825,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>3960.55</v>
+        <v>3950.77</v>
       </c>
     </row>
     <row r="679">
@@ -41886,7 +41886,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>4605.49</v>
+        <v>4594.11</v>
       </c>
     </row>
     <row r="680">
@@ -41947,7 +41947,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>42629.54</v>
+        <v>42524.27</v>
       </c>
     </row>
     <row r="681">
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>4564.24</v>
+        <v>4552.97</v>
       </c>
     </row>
     <row r="682">
@@ -42069,7 +42069,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>2572.02</v>
+        <v>2565.67</v>
       </c>
     </row>
     <row r="683">
@@ -42130,7 +42130,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>28985.64</v>
+        <v>28914.07</v>
       </c>
     </row>
     <row r="684">
@@ -42191,7 +42191,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>13432.47</v>
+        <v>13399.3</v>
       </c>
     </row>
     <row r="685">
@@ -42252,7 +42252,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>1598.14</v>
+        <v>1594.19</v>
       </c>
     </row>
     <row r="686">
@@ -42313,7 +42313,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>6026.56</v>
+        <v>6011.68</v>
       </c>
     </row>
     <row r="687">
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>7216.85</v>
+        <v>7199.03</v>
       </c>
     </row>
     <row r="688">
@@ -42435,7 +42435,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>2795.99</v>
+        <v>2789.09</v>
       </c>
     </row>
     <row r="689">
@@ -42496,7 +42496,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>1489.43</v>
+        <v>1485.75</v>
       </c>
     </row>
     <row r="690">
@@ -42557,7 +42557,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>1111.79</v>
+        <v>1109.04</v>
       </c>
     </row>
     <row r="691">
@@ -42618,7 +42618,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>3033.72</v>
+        <v>3026.23</v>
       </c>
     </row>
     <row r="692">
@@ -42679,7 +42679,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>8355.110000000001</v>
+        <v>8334.48</v>
       </c>
     </row>
     <row r="693">
@@ -42740,7 +42740,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>1016.83</v>
+        <v>1014.32</v>
       </c>
     </row>
     <row r="694">
@@ -42801,7 +42801,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>2540.11</v>
+        <v>2533.84</v>
       </c>
     </row>
     <row r="695">
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>3164.34</v>
+        <v>3156.53</v>
       </c>
     </row>
     <row r="696">
@@ -42923,7 +42923,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2163.81</v>
+        <v>2158.47</v>
       </c>
     </row>
     <row r="697">
@@ -42984,7 +42984,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>2472.67</v>
+        <v>2484.81</v>
       </c>
     </row>
     <row r="698">
@@ -43045,7 +43045,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>1117.19</v>
+        <v>1122.68</v>
       </c>
     </row>
     <row r="699">
@@ -43106,7 +43106,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>1288.43</v>
+        <v>1294.76</v>
       </c>
     </row>
     <row r="700">
@@ -43167,7 +43167,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>3155.45</v>
+        <v>3170.95</v>
       </c>
     </row>
     <row r="701">
@@ -43228,7 +43228,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>1189.34</v>
+        <v>1195.18</v>
       </c>
     </row>
     <row r="702">
@@ -43289,7 +43289,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>871.78</v>
+        <v>876.0599999999999</v>
       </c>
     </row>
     <row r="703">
@@ -43350,7 +43350,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>1455.82</v>
+        <v>1462.97</v>
       </c>
     </row>
     <row r="704">
@@ -43411,7 +43411,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>29007.99</v>
+        <v>29150.49</v>
       </c>
     </row>
     <row r="705">
@@ -43472,7 +43472,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>853.49</v>
+        <v>857.6799999999999</v>
       </c>
     </row>
     <row r="706">
@@ -43533,7 +43533,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>7793.02</v>
+        <v>7831.3</v>
       </c>
     </row>
     <row r="707">
@@ -43594,7 +43594,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>846.66</v>
+        <v>850.8200000000001</v>
       </c>
     </row>
     <row r="708">
@@ -43655,7 +43655,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>6088.19</v>
+        <v>6118.1</v>
       </c>
     </row>
     <row r="709">
@@ -43716,7 +43716,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1670.24</v>
+        <v>1678.45</v>
       </c>
     </row>
     <row r="710">
@@ -43777,7 +43777,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>5154.33</v>
+        <v>5179.65</v>
       </c>
     </row>
     <row r="711">
@@ -43838,7 +43838,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>4280.5</v>
+        <v>4301.52</v>
       </c>
     </row>
     <row r="712">
@@ -43899,7 +43899,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>10785.91</v>
+        <v>10838.89</v>
       </c>
     </row>
     <row r="713">
@@ -43960,7 +43960,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1250.52</v>
+        <v>1256.66</v>
       </c>
     </row>
     <row r="714">
@@ -44021,7 +44021,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>3164.77</v>
+        <v>3180.31</v>
       </c>
     </row>
     <row r="715">
@@ -44082,7 +44082,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>1015.37</v>
+        <v>1020.36</v>
       </c>
     </row>
     <row r="716">
@@ -44143,7 +44143,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2755.24</v>
+        <v>2768.78</v>
       </c>
     </row>
     <row r="717">
@@ -44204,7 +44204,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>5102.36</v>
+        <v>5127.42</v>
       </c>
     </row>
     <row r="718">
@@ -44265,7 +44265,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>26516.98</v>
+        <v>26647.24</v>
       </c>
     </row>
     <row r="719">
@@ -44326,7 +44326,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>1252.26</v>
+        <v>1258.41</v>
       </c>
     </row>
     <row r="720">
@@ -44387,7 +44387,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>1113.91</v>
+        <v>1119.38</v>
       </c>
     </row>
     <row r="721">
@@ -44448,7 +44448,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>1424.82</v>
+        <v>1431.82</v>
       </c>
     </row>
     <row r="722">
@@ -44513,7 +44513,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>255978.28</v>
+        <v>257235.72</v>
       </c>
     </row>
     <row r="723">
@@ -44574,7 +44574,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>1859.54</v>
+        <v>1868.67</v>
       </c>
     </row>
     <row r="724">
@@ -44635,7 +44635,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>3561.6</v>
+        <v>3579.1</v>
       </c>
     </row>
     <row r="725">
@@ -44696,7 +44696,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>4430.8</v>
+        <v>4452.56</v>
       </c>
     </row>
     <row r="726">
@@ -44757,7 +44757,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>22089.9</v>
+        <v>22198.41</v>
       </c>
     </row>
     <row r="727">
@@ -44818,7 +44818,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>50111.52</v>
+        <v>50357.68</v>
       </c>
     </row>
     <row r="728">
@@ -44879,7 +44879,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>3876.09</v>
+        <v>3895.13</v>
       </c>
     </row>
     <row r="729">
@@ -44940,7 +44940,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>1105.05</v>
+        <v>1110.48</v>
       </c>
     </row>
     <row r="730">
@@ -45001,7 +45001,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>1875.76</v>
+        <v>1884.98</v>
       </c>
     </row>
     <row r="731">
@@ -45062,7 +45062,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>938.6</v>
+        <v>943.21</v>
       </c>
     </row>
     <row r="732">
@@ -45123,7 +45123,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>1441.12</v>
+        <v>1448.2</v>
       </c>
     </row>
     <row r="733">
@@ -45184,7 +45184,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>3014.78</v>
+        <v>3029.59</v>
       </c>
     </row>
     <row r="734">
@@ -45245,7 +45245,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>1611.42</v>
+        <v>1619.33</v>
       </c>
     </row>
     <row r="735">
@@ -45306,7 +45306,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>5394.01</v>
+        <v>5420.51</v>
       </c>
     </row>
     <row r="736">
@@ -45367,7 +45367,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>1172.07</v>
+        <v>1177.83</v>
       </c>
     </row>
     <row r="737">
@@ -45428,7 +45428,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>2991.8</v>
+        <v>3006.5</v>
       </c>
     </row>
     <row r="738">
@@ -45489,7 +45489,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>3153.67</v>
+        <v>3169.16</v>
       </c>
     </row>
     <row r="739">
@@ -45550,7 +45550,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>4191.27</v>
+        <v>4211.86</v>
       </c>
     </row>
     <row r="740">
@@ -45611,7 +45611,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>905.4400000000001</v>
+        <v>909.89</v>
       </c>
     </row>
     <row r="741">
@@ -45672,7 +45672,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>3897.56</v>
+        <v>3916.71</v>
       </c>
     </row>
     <row r="742">
@@ -45733,7 +45733,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>1691.19</v>
+        <v>1699.5</v>
       </c>
     </row>
     <row r="743">
@@ -45794,7 +45794,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1786.48</v>
+        <v>1792.4</v>
       </c>
     </row>
     <row r="744">
@@ -45855,7 +45855,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>6325.98</v>
+        <v>6346.97</v>
       </c>
     </row>
     <row r="745">
@@ -45916,7 +45916,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>25001.4</v>
+        <v>25084.34</v>
       </c>
     </row>
     <row r="746">
@@ -45977,7 +45977,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>7313.23</v>
+        <v>7337.49</v>
       </c>
     </row>
     <row r="747">
@@ -46038,7 +46038,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>3558.43</v>
+        <v>3570.24</v>
       </c>
     </row>
     <row r="748">
@@ -46099,7 +46099,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>2155.11</v>
+        <v>2162.26</v>
       </c>
     </row>
     <row r="749">
@@ -46160,7 +46160,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>795.87</v>
+        <v>798.51</v>
       </c>
     </row>
     <row r="750">
@@ -46221,7 +46221,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>8477.15</v>
+        <v>8505.27</v>
       </c>
     </row>
     <row r="751">
@@ -46282,7 +46282,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>1491.9</v>
+        <v>1496.85</v>
       </c>
     </row>
     <row r="752">
@@ -46343,7 +46343,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>2244.57</v>
+        <v>2252.02</v>
       </c>
     </row>
     <row r="753">
@@ -46404,7 +46404,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>968.86</v>
+        <v>972.08</v>
       </c>
     </row>
     <row r="754">
@@ -46465,7 +46465,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>2034.1</v>
+        <v>2040.85</v>
       </c>
     </row>
     <row r="755">
@@ -46526,7 +46526,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>6867.13</v>
+        <v>6889.91</v>
       </c>
     </row>
     <row r="756">
@@ -46587,7 +46587,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>1743.89</v>
+        <v>1749.68</v>
       </c>
     </row>
     <row r="757">
@@ -46648,7 +46648,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>13333.16</v>
+        <v>13377.39</v>
       </c>
     </row>
     <row r="758">
@@ -46709,7 +46709,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>4088.02</v>
+        <v>4101.58</v>
       </c>
     </row>
     <row r="759">
@@ -46770,7 +46770,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>3833.53</v>
+        <v>3846.25</v>
       </c>
     </row>
     <row r="760">
@@ -46831,7 +46831,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>1003.36</v>
+        <v>1006.68</v>
       </c>
     </row>
     <row r="761">
@@ -46892,7 +46892,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>930.01</v>
+        <v>933.09</v>
       </c>
     </row>
     <row r="762">
@@ -46953,7 +46953,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>1812.21</v>
+        <v>1818.22</v>
       </c>
     </row>
     <row r="763">
@@ -47014,7 +47014,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>19464.91</v>
+        <v>19529.48</v>
       </c>
     </row>
     <row r="764">
@@ -47075,7 +47075,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>2156.25</v>
+        <v>2163.41</v>
       </c>
     </row>
     <row r="765">
@@ -47136,7 +47136,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>15673.76</v>
+        <v>15725.75</v>
       </c>
     </row>
     <row r="766">
@@ -47197,7 +47197,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>798.08</v>
+        <v>800.73</v>
       </c>
     </row>
     <row r="767">
@@ -47258,7 +47258,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>9210.629999999999</v>
+        <v>9241.18</v>
       </c>
     </row>
     <row r="768">
@@ -47319,7 +47319,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>890.77</v>
+        <v>893.72</v>
       </c>
     </row>
     <row r="769">
@@ -47380,7 +47380,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>1433.12</v>
+        <v>1437.88</v>
       </c>
     </row>
     <row r="770">
@@ -47441,7 +47441,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>1750.06</v>
+        <v>1755.86</v>
       </c>
     </row>
     <row r="771">
@@ -47502,7 +47502,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>912.51</v>
+        <v>915.54</v>
       </c>
     </row>
     <row r="772">
@@ -47563,7 +47563,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>3082.58</v>
+        <v>3092.81</v>
       </c>
     </row>
     <row r="773">
@@ -47624,7 +47624,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>1101.95</v>
+        <v>1105.6</v>
       </c>
     </row>
     <row r="774">
@@ -47685,7 +47685,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>6117.03</v>
+        <v>6137.32</v>
       </c>
     </row>
     <row r="775">
@@ -47746,7 +47746,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>2879.7</v>
+        <v>2889.25</v>
       </c>
     </row>
     <row r="776">
@@ -47807,7 +47807,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>5759.11</v>
+        <v>5778.22</v>
       </c>
     </row>
     <row r="777">
@@ -47868,7 +47868,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>15176.63</v>
+        <v>15226.98</v>
       </c>
     </row>
     <row r="778">
@@ -47929,7 +47929,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>3871.63</v>
+        <v>3884.48</v>
       </c>
     </row>
     <row r="779">
@@ -47990,7 +47990,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>1238.98</v>
+        <v>1243.09</v>
       </c>
     </row>
     <row r="780">
@@ -48051,7 +48051,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>8053.17</v>
+        <v>8079.88</v>
       </c>
     </row>
     <row r="781">
@@ -48112,7 +48112,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>1190.82</v>
+        <v>1194.78</v>
       </c>
     </row>
     <row r="782">
@@ -48173,7 +48173,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>3689.64</v>
+        <v>3701.88</v>
       </c>
     </row>
     <row r="783">
@@ -48234,7 +48234,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>1211.62</v>
+        <v>1215.64</v>
       </c>
     </row>
     <row r="784">
@@ -48295,7 +48295,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>800.4299999999999</v>
+        <v>803.08</v>
       </c>
     </row>
     <row r="785">
@@ -48356,7 +48356,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>6172.09</v>
+        <v>6192.56</v>
       </c>
     </row>
     <row r="786">
@@ -48417,7 +48417,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>2107.17</v>
+        <v>2114.16</v>
       </c>
     </row>
     <row r="787">
@@ -48478,7 +48478,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>2000.3</v>
+        <v>2006.93</v>
       </c>
     </row>
     <row r="788">
@@ -48539,7 +48539,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>836.74</v>
+        <v>839.52</v>
       </c>
     </row>
     <row r="789">
@@ -48600,7 +48600,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>1120.89</v>
+        <v>1124.61</v>
       </c>
     </row>
     <row r="790">
@@ -48661,7 +48661,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>3909.79</v>
+        <v>3922.76</v>
       </c>
     </row>
     <row r="791">
@@ -48722,7 +48722,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>1301.87</v>
+        <v>1306.19</v>
       </c>
     </row>
     <row r="792">
@@ -48783,7 +48783,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>2829.43</v>
+        <v>2838.82</v>
       </c>
     </row>
     <row r="793">
@@ -48844,7 +48844,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>1194.87</v>
+        <v>1198.83</v>
       </c>
     </row>
     <row r="794">
@@ -48905,7 +48905,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>3335.88</v>
+        <v>3346.95</v>
       </c>
     </row>
     <row r="795">
@@ -48966,7 +48966,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>2360.71</v>
+        <v>2368.55</v>
       </c>
     </row>
     <row r="796">
@@ -49027,7 +49027,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>7781.38</v>
+        <v>7807.19</v>
       </c>
     </row>
     <row r="797">
@@ -49088,7 +49088,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>1219.56</v>
+        <v>1223.61</v>
       </c>
     </row>
     <row r="798">
@@ -49149,7 +49149,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>4717.91</v>
+        <v>4732.92</v>
       </c>
     </row>
     <row r="799">
@@ -49210,7 +49210,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>787.95</v>
+        <v>790.46</v>
       </c>
     </row>
     <row r="800">
@@ -49271,7 +49271,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>7759.03</v>
+        <v>7783.73</v>
       </c>
     </row>
     <row r="801">
@@ -49332,7 +49332,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>21638.1</v>
+        <v>21706.97</v>
       </c>
     </row>
     <row r="802">
@@ -49393,7 +49393,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>6513.57</v>
+        <v>6534.3</v>
       </c>
     </row>
     <row r="803">
@@ -49454,7 +49454,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>4277.93</v>
+        <v>4291.54</v>
       </c>
     </row>
     <row r="804">
@@ -49515,7 +49515,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>2578.33</v>
+        <v>2586.53</v>
       </c>
     </row>
     <row r="805">
@@ -49576,7 +49576,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>8181.59</v>
+        <v>8207.629999999999</v>
       </c>
     </row>
     <row r="806">
@@ -49637,7 +49637,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>32568.77</v>
+        <v>32672.43</v>
       </c>
     </row>
     <row r="807">
@@ -49698,7 +49698,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>802.61</v>
+        <v>805.17</v>
       </c>
     </row>
     <row r="808">
@@ -49759,7 +49759,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>2192.45</v>
+        <v>2199.42</v>
       </c>
     </row>
     <row r="809">
@@ -49820,7 +49820,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>38990.25</v>
+        <v>39114.34</v>
       </c>
     </row>
     <row r="810">
@@ -49881,7 +49881,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>27359.82</v>
+        <v>27446.9</v>
       </c>
     </row>
     <row r="811">
@@ -49942,7 +49942,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>3477.01</v>
+        <v>3488.08</v>
       </c>
     </row>
     <row r="812">
@@ -50003,7 +50003,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>1633.92</v>
+        <v>1639.12</v>
       </c>
     </row>
     <row r="813">
@@ -50064,7 +50064,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>1140.1</v>
+        <v>1143.73</v>
       </c>
     </row>
     <row r="814">
@@ -50125,7 +50125,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>1228.52</v>
+        <v>1232.43</v>
       </c>
     </row>
     <row r="815">
@@ -50186,7 +50186,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>3406.2</v>
+        <v>3417.04</v>
       </c>
     </row>
     <row r="816">
@@ -50247,7 +50247,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>50434.8</v>
+        <v>50595.32</v>
       </c>
     </row>
     <row r="817">
@@ -50308,7 +50308,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>2304.07</v>
+        <v>2311.4</v>
       </c>
     </row>
     <row r="818">
@@ -50369,7 +50369,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>787.08</v>
+        <v>789.59</v>
       </c>
     </row>
     <row r="819">
@@ -50430,7 +50430,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>847.3099999999999</v>
+        <v>850.01</v>
       </c>
     </row>
     <row r="820">
@@ -50491,7 +50491,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>6846.31</v>
+        <v>6868.1</v>
       </c>
     </row>
     <row r="821">
@@ -50552,7 +50552,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>820.78</v>
+        <v>823.39</v>
       </c>
     </row>
     <row r="822">
@@ -50613,7 +50613,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>1628.04</v>
+        <v>1633.22</v>
       </c>
     </row>
     <row r="823">
@@ -50674,7 +50674,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>26436.61</v>
+        <v>26520.75</v>
       </c>
     </row>
     <row r="824">
@@ -50735,7 +50735,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>793.27</v>
+        <v>795.8</v>
       </c>
     </row>
     <row r="825">
@@ -50796,7 +50796,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>1588.76</v>
+        <v>1593.82</v>
       </c>
     </row>
     <row r="826">
@@ -50857,7 +50857,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>2770.63</v>
+        <v>2779.44</v>
       </c>
     </row>
     <row r="827">
@@ -50918,7 +50918,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>5099.82</v>
+        <v>5116.05</v>
       </c>
     </row>
     <row r="828">
@@ -50979,7 +50979,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>1771.34</v>
+        <v>1776.97</v>
       </c>
     </row>
     <row r="829">
@@ -51040,7 +51040,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>3377.84</v>
+        <v>3388.59</v>
       </c>
     </row>
     <row r="830">
@@ -51101,7 +51101,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>877.13</v>
+        <v>879.92</v>
       </c>
     </row>
     <row r="831">
@@ -51162,7 +51162,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>2954.39</v>
+        <v>2963.8</v>
       </c>
     </row>
     <row r="832">
@@ -51223,7 +51223,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>21558.33</v>
+        <v>21626.95</v>
       </c>
     </row>
     <row r="833">
@@ -51284,7 +51284,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>2467.08</v>
+        <v>2474.93</v>
       </c>
     </row>
     <row r="834">
@@ -51345,7 +51345,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>3284.52</v>
+        <v>3294.97</v>
       </c>
     </row>
     <row r="835">
@@ -51406,7 +51406,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>2781.71</v>
+        <v>2790.56</v>
       </c>
     </row>
     <row r="836">
@@ -51467,7 +51467,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>22191.05</v>
+        <v>22261.68</v>
       </c>
     </row>
     <row r="837">
@@ -51528,7 +51528,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>4991.76</v>
+        <v>5018.3</v>
       </c>
     </row>
     <row r="838">
@@ -51589,7 +51589,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>989.08</v>
+        <v>994.34</v>
       </c>
     </row>
     <row r="839">
@@ -51650,7 +51650,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>19154.13</v>
+        <v>19255.99</v>
       </c>
     </row>
     <row r="840">
@@ -51711,7 +51711,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>1142.75</v>
+        <v>1148.83</v>
       </c>
     </row>
     <row r="841">
@@ -51772,7 +51772,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>1216.43</v>
+        <v>1222.89</v>
       </c>
     </row>
     <row r="842">
@@ -51833,7 +51833,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>1499.51</v>
+        <v>1507.48</v>
       </c>
     </row>
     <row r="843">
@@ -51894,7 +51894,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>12745.67</v>
+        <v>12813.45</v>
       </c>
     </row>
     <row r="844">
@@ -51955,7 +51955,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>1180.52</v>
+        <v>1186.8</v>
       </c>
     </row>
     <row r="845">
@@ -52016,7 +52016,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>2127.52</v>
+        <v>2138.84</v>
       </c>
     </row>
     <row r="846">
@@ -52077,7 +52077,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>1422.61</v>
+        <v>1430.18</v>
       </c>
     </row>
     <row r="847">
@@ -52138,7 +52138,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>11171.02</v>
+        <v>11230.43</v>
       </c>
     </row>
     <row r="848">
@@ -52199,7 +52199,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>1472.84</v>
+        <v>1480.68</v>
       </c>
     </row>
     <row r="849">
@@ -52260,7 +52260,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>867.37</v>
+        <v>871.99</v>
       </c>
     </row>
     <row r="850">
@@ -52321,7 +52321,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>4597.27</v>
+        <v>4621.71</v>
       </c>
     </row>
     <row r="851">
@@ -52382,7 +52382,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>1610.76</v>
+        <v>1619.32</v>
       </c>
     </row>
     <row r="852">
@@ -52443,7 +52443,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>2785.2</v>
+        <v>2800.01</v>
       </c>
     </row>
     <row r="853">
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>53452.29</v>
+        <v>53736.52</v>
       </c>
     </row>
     <row r="854">
@@ -52565,7 +52565,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>1813.38</v>
+        <v>1823.02</v>
       </c>
     </row>
     <row r="855">
@@ -52626,7 +52626,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>2212.35</v>
+        <v>2224.11</v>
       </c>
     </row>
     <row r="856">
@@ -52687,7 +52687,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>1530.45</v>
+        <v>1538.59</v>
       </c>
     </row>
     <row r="857">
@@ -52748,7 +52748,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>2461.43</v>
+        <v>2474.52</v>
       </c>
     </row>
     <row r="858">
@@ -52809,7 +52809,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>1408.61</v>
+        <v>1416.1</v>
       </c>
     </row>
     <row r="859">
@@ -52870,7 +52870,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>919.84</v>
+        <v>924.73</v>
       </c>
     </row>
     <row r="860">
@@ -52931,7 +52931,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>85131.25</v>
+        <v>85583.94</v>
       </c>
     </row>
     <row r="861">
@@ -52992,7 +52992,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>1869.93</v>
+        <v>1879.87</v>
       </c>
     </row>
     <row r="862">
@@ -53053,7 +53053,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>2891.89</v>
+        <v>2907.26</v>
       </c>
     </row>
     <row r="863">
@@ -53114,7 +53114,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>3884.61</v>
+        <v>3905.26</v>
       </c>
     </row>
     <row r="864">
@@ -53175,7 +53175,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>3954.57</v>
+        <v>3975.6</v>
       </c>
     </row>
     <row r="865">
@@ -53236,7 +53236,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>10595.01</v>
+        <v>10651.35</v>
       </c>
     </row>
     <row r="866">
@@ -53297,7 +53297,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>842.8099999999999</v>
+        <v>847.3</v>
       </c>
     </row>
     <row r="867">
@@ -53358,7 +53358,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>904.04</v>
+        <v>908.85</v>
       </c>
     </row>
     <row r="868">
@@ -53419,7 +53419,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>1014</v>
+        <v>1019.39</v>
       </c>
     </row>
     <row r="869">
@@ -53480,7 +53480,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>813.67</v>
+        <v>818</v>
       </c>
     </row>
     <row r="870">
@@ -53541,7 +53541,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>2699.84</v>
+        <v>2714.2</v>
       </c>
     </row>
     <row r="871">
@@ -53602,7 +53602,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>1120.27</v>
+        <v>1126.23</v>
       </c>
     </row>
     <row r="872">
@@ -53663,7 +53663,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>1999.08</v>
+        <v>2009.71</v>
       </c>
     </row>
     <row r="873">
@@ -53724,7 +53724,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>20829.5</v>
+        <v>20940.26</v>
       </c>
     </row>
     <row r="874">
@@ -53785,7 +53785,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>1948.78</v>
+        <v>1959.14</v>
       </c>
     </row>
     <row r="875">
@@ -53846,7 +53846,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>1811.39</v>
+        <v>1821.02</v>
       </c>
     </row>
     <row r="876">
@@ -53907,7 +53907,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>4527.27</v>
+        <v>4551.34</v>
       </c>
     </row>
     <row r="877">
@@ -53968,7 +53968,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>13436.96</v>
+        <v>13508.41</v>
       </c>
     </row>
     <row r="878">
@@ -54029,7 +54029,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>28575.23</v>
+        <v>28727.18</v>
       </c>
     </row>
     <row r="879">
@@ -54090,7 +54090,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>14471.42</v>
+        <v>14548.37</v>
       </c>
     </row>
     <row r="880">
@@ -54151,7 +54151,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>20371.76</v>
+        <v>20480.09</v>
       </c>
     </row>
     <row r="881">
@@ -54212,7 +54212,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>844.7</v>
+        <v>849.1900000000001</v>
       </c>
     </row>
     <row r="882">
@@ -54273,7 +54273,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>2102.33</v>
+        <v>2113.51</v>
       </c>
     </row>
     <row r="883">
@@ -54334,7 +54334,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>40768.37</v>
+        <v>40985.16</v>
       </c>
     </row>
     <row r="884">
@@ -54395,7 +54395,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>16453.59</v>
+        <v>16541.08</v>
       </c>
     </row>
     <row r="885">
@@ -54456,7 +54456,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>1674.77</v>
+        <v>1683.68</v>
       </c>
     </row>
     <row r="886">
@@ -54517,7 +54517,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>5437.6</v>
+        <v>5466.52</v>
       </c>
     </row>
     <row r="887">
@@ -54578,7 +54578,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>7916.9</v>
+        <v>7959</v>
       </c>
     </row>
     <row r="888">
@@ -54639,7 +54639,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>2512.47</v>
+        <v>2525.83</v>
       </c>
     </row>
     <row r="889">
@@ -54700,7 +54700,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>4232.7</v>
+        <v>4255.21</v>
       </c>
     </row>
     <row r="890">
@@ -54761,7 +54761,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>4117.1</v>
+        <v>4138.99</v>
       </c>
     </row>
     <row r="891">
@@ -54822,7 +54822,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>10523.42</v>
+        <v>10579.38</v>
       </c>
     </row>
     <row r="892">
@@ -54883,7 +54883,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>843.8200000000001</v>
+        <v>848.3099999999999</v>
       </c>
     </row>
     <row r="893">
@@ -54944,7 +54944,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>4726.82</v>
+        <v>4751.95</v>
       </c>
     </row>
     <row r="894">
@@ -55005,7 +55005,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>2559.01</v>
+        <v>2572.61</v>
       </c>
     </row>
     <row r="895">
@@ -55066,7 +55066,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>2176.14</v>
+        <v>2187.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23062,7 +23062,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26863,7 +26863,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -26974,7 +26974,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27096,7 +27096,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -28072,7 +28072,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28087,7 +28087,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -29479,7 +29479,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -30516,7 +30516,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30638,7 +30638,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31629,7 +31629,7 @@
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
@@ -31679,7 +31679,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -32289,7 +32289,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -33570,7 +33570,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33814,7 +33814,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -34485,7 +34485,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -35095,7 +35095,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35156,7 +35156,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35339,7 +35339,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35583,7 +35583,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -37413,7 +37413,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37901,7 +37901,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37962,7 +37962,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38023,7 +38023,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38145,7 +38145,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38267,7 +38267,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38511,7 +38511,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38999,7 +38999,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39121,7 +39121,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39670,7 +39670,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39853,7 +39853,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40768,7 +40768,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -41256,7 +41256,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41622,7 +41622,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -42110,7 +42110,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -43147,7 +43147,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43818,7 +43818,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -44001,7 +44001,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44504,7 +44504,7 @@
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
@@ -44676,7 +44676,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44798,7 +44798,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -45225,7 +45225,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45469,7 +45469,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45591,7 +45591,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -46018,7 +46018,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46079,7 +46079,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46140,7 +46140,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46506,7 +46506,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46994,7 +46994,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47177,7 +47177,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47482,7 +47482,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -48580,7 +48580,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -48946,7 +48946,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -49068,7 +49068,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -49129,7 +49129,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -50227,7 +50227,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -51691,7 +51691,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -51996,7 +51996,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -52057,7 +52057,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -52179,7 +52179,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -53216,7 +53216,7 @@
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I865" t="inlineStr">
@@ -53277,7 +53277,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -53460,7 +53460,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -53521,7 +53521,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -53582,7 +53582,7 @@
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
@@ -54497,7 +54497,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54558,7 +54558,7 @@
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile C.D.P. Santiago Sur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORPORACION SOCIAL Y CULTURAL DE CONCEPCION- SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Escuadrilla de Abastecimiento del Edificio FF.AA.</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11955,17 +11955,17 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE TALCAHUANO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Economato CPF San Miguel</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA CAMPO MILITAR PENALOLEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -19163,7 +19163,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19824,12 +19824,12 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ÑUBLE DEL SERVICIO DE REGISTRO CIVIL E IDENTIFIC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19885,12 +19885,12 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ÑUBLE DEL SERVICIO DE REGISTRO CIVIL E IDENTIFIC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Economato</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Said Mauricio Tarzijan Julian</t>
+          <t>SAID MAURICIO TARZIJAN JULIAN</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO ANDRES </t>
+          <t xml:space="preserve">Eduardo Andres </t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20993,7 +20993,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>IMPO PAPER SPA</t>
+          <t>Impo Paper Spa</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -22813,7 +22813,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Mineduc Administración X Región</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificacion</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24653,7 +24653,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>INGESCOM LTDA.</t>
+          <t>Ingescom ltda.</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25629,7 +25629,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27035,7 +27035,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27223,7 +27223,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -27467,7 +27467,7 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -27772,7 +27772,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -28437,7 +28437,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28813,7 +28813,7 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -28996,7 +28996,7 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -29108,7 +29108,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -29291,7 +29291,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29657,7 +29657,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -29840,7 +29840,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -30389,7 +30389,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30521,7 +30521,7 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -30572,7 +30572,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -30633,7 +30633,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -30938,7 +30938,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -31131,7 +31131,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -31192,7 +31192,7 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -31375,7 +31375,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
@@ -31426,7 +31426,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Femenino Semiabierto St</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -31497,7 +31497,7 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -32223,7 +32223,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -32416,7 +32416,7 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -32467,7 +32467,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -32843,7 +32843,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -32955,7 +32955,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -33077,7 +33077,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Economato C.C.P. Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33087,7 +33087,7 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33209,7 +33209,7 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -33260,7 +33260,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -33311,7 +33311,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -33321,7 +33321,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -33504,7 +33504,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33809,7 +33809,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -33880,7 +33880,7 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
@@ -33941,7 +33941,7 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
@@ -34297,7 +34297,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -34490,7 +34490,7 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
@@ -34785,7 +34785,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -34846,7 +34846,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Salud</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -35273,12 +35273,12 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35639,7 +35639,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Pinto Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -35761,7 +35761,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LLANQUIHUE-DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -35954,7 +35954,7 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J589" t="inlineStr">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -37408,7 +37408,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -37530,7 +37530,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -37713,7 +37713,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -37845,7 +37845,7 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
@@ -38272,7 +38272,7 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
@@ -38333,7 +38333,7 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -39116,7 +39116,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39238,7 +39238,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>SERPLAC III Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -39726,12 +39726,12 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39787,7 +39787,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -40031,7 +40031,7 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -40336,7 +40336,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -40519,7 +40519,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -40646,7 +40646,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40834,7 +40834,7 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>Avalco SpA</t>
+          <t>AVALCO SPA</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
@@ -40946,7 +40946,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -41068,7 +41068,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -41190,7 +41190,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -41561,7 +41561,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41617,7 +41617,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -41739,7 +41739,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -41922,7 +41922,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -42227,7 +42227,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -42293,7 +42293,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42969,7 +42969,7 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
@@ -43203,12 +43203,12 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA PESCA ARTESANAL Y A</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43569,7 +43569,7 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -44179,12 +44179,12 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -44549,7 +44549,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -44859,7 +44859,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -45037,7 +45037,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -45098,7 +45098,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>MACRO-ZONA DE SALUD SANTIAGO CENTRO SUR</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -45108,7 +45108,7 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
@@ -45342,7 +45342,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -45403,7 +45403,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -45464,7 +45464,7 @@
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -45525,7 +45525,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -45952,7 +45952,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -46562,7 +46562,7 @@
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -46623,12 +46623,12 @@
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46867,7 +46867,7 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
+          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -47121,7 +47121,7 @@
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -47360,7 +47360,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47477,7 +47477,7 @@
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -47543,7 +47543,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47670,7 +47670,7 @@
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -47904,7 +47904,7 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -47914,7 +47914,7 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
@@ -48031,7 +48031,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48270,7 +48270,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -48331,7 +48331,7 @@
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -48392,7 +48392,7 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -48458,12 +48458,12 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J787" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -48768,7 +48768,7 @@
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
@@ -49073,7 +49073,7 @@
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
@@ -49185,7 +49185,7 @@
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>Delegación Provincial Chiloe</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
@@ -49734,7 +49734,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -49978,7 +49978,7 @@
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -50105,7 +50105,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -50466,17 +50466,17 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J820" t="inlineStr">
@@ -50532,12 +50532,12 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
@@ -50578,7 +50578,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F822" t="inlineStr">
@@ -50654,7 +50654,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -50710,7 +50710,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -50771,7 +50771,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
@@ -50893,7 +50893,7 @@
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
@@ -50903,7 +50903,7 @@
       </c>
       <c r="I827" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J827" t="inlineStr">
@@ -50954,7 +50954,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -51025,7 +51025,7 @@
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J829" t="inlineStr">
@@ -51081,12 +51081,12 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J830" t="inlineStr">
@@ -51137,7 +51137,7 @@
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
@@ -51442,7 +51442,7 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
@@ -51625,7 +51625,7 @@
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
@@ -51686,7 +51686,7 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -51869,7 +51869,7 @@
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública de Los Liberta</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
@@ -52113,7 +52113,7 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública de Los Liberta</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -52235,7 +52235,7 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Adulto Mayor</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -52296,7 +52296,7 @@
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
@@ -52469,7 +52469,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
@@ -52479,7 +52479,7 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
@@ -52540,7 +52540,7 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>DIRECCION DE INFANCIA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
@@ -52550,7 +52550,7 @@
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J854" t="inlineStr">
@@ -52601,7 +52601,7 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
@@ -52662,7 +52662,7 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
@@ -52723,7 +52723,7 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -52906,7 +52906,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
@@ -53333,7 +53333,7 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -53394,7 +53394,7 @@
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
@@ -53577,7 +53577,7 @@
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H871" t="inlineStr">
@@ -54014,7 +54014,7 @@
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J878" t="inlineStr">
@@ -54126,7 +54126,7 @@
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
@@ -54187,7 +54187,7 @@
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
@@ -54431,7 +54431,7 @@
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
@@ -54492,7 +54492,7 @@
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
@@ -54624,7 +54624,7 @@
       </c>
       <c r="I888" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J888" t="inlineStr">
@@ -54685,7 +54685,7 @@
       </c>
       <c r="I889" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J889" t="inlineStr">
@@ -54741,7 +54741,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -54797,12 +54797,12 @@
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -54848,7 +54848,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
@@ -54858,7 +54858,7 @@
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1647,7 +1651,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3435,7 +3443,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3626,7 +3638,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4646,7 +4662,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4768,7 +4788,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4951,7 +4975,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5203,7 +5231,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5581,7 +5613,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5902,7 +5938,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6028,7 +6068,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6475,7 +6519,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6649,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6983,7 +7035,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7239,7 +7295,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7365,7 +7425,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7747,7 +7811,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8133,7 +8201,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8515,7 +8587,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10112,7 +10188,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10559,7 +10639,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10681,7 +10765,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10742,7 +10830,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10803,7 +10895,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11124,7 +11220,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11766,7 +11866,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12565,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13855,7 +13963,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14489,7 +14601,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15127,7 +15243,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15314,7 +15434,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15700,7 +15824,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16464,7 +16592,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16716,7 +16848,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16842,7 +16978,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17155,7 +17295,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17472,7 +17616,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17598,7 +17746,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17789,7 +17941,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18935,7 +19091,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18996,7 +19156,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19382,7 +19546,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19508,7 +19676,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21357,7 +21529,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21865,7 +22041,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22052,7 +22232,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22690,7 +22874,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22946,7 +23134,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23007,7 +23199,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23515,7 +23711,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23706,7 +23906,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25685,7 +25889,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26514,7 +26722,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27469,7 +27681,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28749,7 +28965,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29062,7 +29282,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30155,7 +30379,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30338,7 +30566,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32642,7 +32874,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32703,7 +32939,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32890,7 +33130,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33967,7 +34211,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34093,7 +34341,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34601,7 +34853,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34723,7 +34979,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35556,7 +35816,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35873,7 +36137,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +36397,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36580,7 +36852,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37669,7 +37945,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40172,7 +40452,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45040,7 +45324,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47283,7 +47571,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47474,7 +47766,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49973,7 +50269,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50229,7 +50529,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51127,7 +51431,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51444,7 +51752,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52911,7 +53223,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53358,7 +53674,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L830" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57328,7 +57648,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
